--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608E9D54-F0D2-B044-90A2-C9DA8C7AB68A}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B5B4A0-394E-FA4E-835E-3081B2C74CCD}"/>
   <bookViews>
-    <workbookView xWindow="-34060" yWindow="1600" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30820" yWindow="1980" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
   <si>
     <t>Año</t>
   </si>
@@ -404,15 +404,37 @@
   </si>
   <si>
     <t>IEEE: The Role of Spain in the AI Revolution</t>
+  </si>
+  <si>
+    <t>Introducción al prompting, aspectos técnicos y económicos de la IA. Ejemplos con Copilot</t>
+  </si>
+  <si>
+    <t>Introduction to prompting, technical and echonomical aspects of AI. Examples with Copilot</t>
+  </si>
+  <si>
+    <t>Pfizer</t>
+  </si>
+  <si>
+    <t>1 hour</t>
+  </si>
+  <si>
+    <t>Impact of AI on the environment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -538,75 +560,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1934,11 +1960,51 @@
       </c>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J41" s="23"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J42" s="23"/>
+    <row r="41" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="11">
+        <v>2026</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="J43" s="23"/>

--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B5B4A0-394E-FA4E-835E-3081B2C74CCD}"/>
+  <xr:revisionPtr revIDLastSave="453" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A941CAD0-157E-ED45-9D10-1B7463BB1296}"/>
   <bookViews>
     <workbookView xWindow="-30820" yWindow="1980" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="134">
   <si>
     <t>Año</t>
   </si>
@@ -419,15 +419,28 @@
   </si>
   <si>
     <t>Impact of AI on the environment</t>
+  </si>
+  <si>
+    <t>International Specialization Programme in Project Administration (iXPA) (V Edición)</t>
+  </si>
+  <si>
+    <t>International Specialization Programme in Project Administration (V Edition)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -560,75 +573,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -638,10 +655,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -947,7 +964,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AF44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="15" customWidth="1"/>
@@ -2006,8 +2023,33 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J43" s="23"/>
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K43" s="25"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B44" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="453" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A941CAD0-157E-ED45-9D10-1B7463BB1296}"/>
+  <xr:revisionPtr revIDLastSave="457" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36DB55E-A353-4E40-A698-65540027843F}"/>
   <bookViews>
-    <workbookView xWindow="-30820" yWindow="1980" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="136">
   <si>
     <t>Año</t>
   </si>
@@ -425,15 +425,28 @@
   </si>
   <si>
     <t>International Specialization Programme in Project Administration (V Edition)</t>
+  </si>
+  <si>
+    <t>Programación de software asistida con IA.</t>
+  </si>
+  <si>
+    <t>Software Programming assisted with AI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -575,73 +588,77 @@
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -652,12 +669,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2027,10 +2038,10 @@
       <c r="A43" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" s="33" t="s">
         <v>133</v>
       </c>
       <c r="E43" s="10">
@@ -2048,8 +2059,29 @@
       </c>
       <c r="K43" s="25"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B44" s="33"/>
+    <row r="44" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="23" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/External_Courses_Events_Lectures.xlsx
+++ b/data/External_Courses_Events_Lectures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Eventos/Congresos_Ponencias_Hackathones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="457" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36DB55E-A353-4E40-A698-65540027843F}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C81314FA-A59B-FE46-A046-A2B9C50303B1}"/>
   <bookViews>
     <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="144">
   <si>
     <t>Año</t>
   </si>
@@ -431,15 +431,46 @@
   </si>
   <si>
     <t>Software Programming assisted with AI</t>
+  </si>
+  <si>
+    <t>Democratizing Psycholinguistic Norm Generation with Large Language Models</t>
+  </si>
+  <si>
+    <t>Democratizando la Generación de normas psicolingüísticas con Grandes Modelos de Lenguaje</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t>Boston, USA</t>
+  </si>
+  <si>
+    <t>Desarrollo de propuestas de proyectos europeas usando herramientas de IA</t>
+  </si>
+  <si>
+    <t>Developing European AI proposals with AI tools</t>
+  </si>
+  <si>
+    <t>Univeristy of Jaen</t>
+  </si>
+  <si>
+    <t>Jaen, Spain</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -586,75 +617,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -665,11 +700,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -975,7 +1010,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="15" customWidth="1"/>
@@ -2083,6 +2118,58 @@
         <v>109</v>
       </c>
     </row>
+    <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A46" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="G46" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="H46" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
